--- a/artfynd/A 67855-2021 artfynd.xlsx
+++ b/artfynd/A 67855-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67855-2021 artfynd.xlsx
+++ b/artfynd/A 67855-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69517693</v>
+        <v>75803204</v>
       </c>
       <c r="B2" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4189</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lyssnarberget, intill NR, Upl</t>
+          <t>Däcksta 2,5 km S om Hökhuvud, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>678259.2181276781</v>
+        <v>678091</v>
       </c>
       <c r="R2" t="n">
-        <v>6677693.663641705</v>
+        <v>6677542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-08-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-07-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 fjolårs-ex. i barrmatta under gran.</t>
+          <t>På stort stenblock.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stort stenblock.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75940911</v>
+        <v>69517690</v>
       </c>
       <c r="B3" t="n">
-        <v>90366</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5836</v>
+        <v>4188</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,14 +822,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lyssnarberget, intill NR, Upl</t>
+          <t>Lyssnarbergets NR, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678188.9508678119</v>
+        <v>678127</v>
       </c>
       <c r="R3" t="n">
-        <v>6677712.649854265</v>
+        <v>6677842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,24 +859,14 @@
           <t>1999-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-08-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 ex. i äldre, örtrik granskog.</t>
+          <t>Ca. 10 fjolårs-ex. i barrmatta under gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,11 +877,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,6 +890,571 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69517692</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lyssnarbergets NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>678108</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6677822</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 fjolårs-ex. i barrmatta under gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69517693</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lyssnarberget, intill NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>678259</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6677694</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 fjolårs-ex. i barrmatta under gran.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>75905835</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lyssnarbergets NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>678117</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6677832</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>75940911</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lyssnarberget, intill NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>678189</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6677713</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 ex. i äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>75940934</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Däcksta 2,5 km S om Hökhuvud, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>678081</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6677522</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1999-08-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 ex. i äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67855-2021 artfynd.xlsx
+++ b/artfynd/A 67855-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75803204</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69517690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69517692</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69517693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75905835</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75940911</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,8 +1490,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75940934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>